--- a/artfynd/A 21926-2023 artfynd.xlsx
+++ b/artfynd/A 21926-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21926-2023 artfynd.xlsx
+++ b/artfynd/A 21926-2023 artfynd.xlsx
@@ -675,44 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109996845</v>
+        <v>110023751</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -720,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533396.070554397</v>
+        <v>533320</v>
       </c>
       <c r="R2" t="n">
-        <v>6707159.886212878</v>
+        <v>6707225</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +776,7 @@
         <v>109996780</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533403.8413364878</v>
+        <v>533403</v>
       </c>
       <c r="R3" t="n">
-        <v>6707120.047891806</v>
+        <v>6707121</v>
       </c>
       <c r="S3" t="n">
         <v>14</v>
@@ -870,19 +846,9 @@
           <t>2023-06-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +875,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109997010</v>
+        <v>109996845</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,7 +905,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -954,13 +915,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533385.8598680623</v>
+        <v>533397</v>
       </c>
       <c r="R4" t="n">
-        <v>6707196.745327558</v>
+        <v>6707160</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,19 +948,9 @@
           <t>2023-06-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-06-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +977,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110023596</v>
+        <v>109996964</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1061,7 +1007,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1071,13 +1017,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533364.5223626038</v>
+        <v>533386</v>
       </c>
       <c r="R5" t="n">
-        <v>6707209.358818708</v>
+        <v>6707197</v>
       </c>
       <c r="S5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,22 +1047,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110023980</v>
+        <v>110022988</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1109,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1188,13 +1119,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533282.1935690296</v>
+        <v>533441</v>
       </c>
       <c r="R6" t="n">
-        <v>6707253.436264393</v>
+        <v>6707136</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,19 +1152,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110023746</v>
+        <v>110023249</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1211,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1305,13 +1221,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533319.4667128013</v>
+        <v>533438</v>
       </c>
       <c r="R7" t="n">
-        <v>6707225.202711429</v>
+        <v>6707164</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,19 +1254,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,15 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110024680</v>
+        <v>110023546</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1313,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1422,13 +1323,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533337.0514982155</v>
+        <v>533400</v>
       </c>
       <c r="R8" t="n">
-        <v>6707191.367948272</v>
+        <v>6707188</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,19 +1356,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,15 +1385,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110024517</v>
+        <v>110023596</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1415,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1539,13 +1425,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533291.4251737468</v>
+        <v>533365</v>
       </c>
       <c r="R9" t="n">
-        <v>6707215.583032044</v>
+        <v>6707209</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1572,19 +1458,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,40 +1487,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110023751</v>
+        <v>110023746</v>
       </c>
       <c r="B10" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1652,10 +1527,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533319.4667128013</v>
+        <v>533320</v>
       </c>
       <c r="R10" t="n">
-        <v>6707225.202711429</v>
+        <v>6707225</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1685,19 +1560,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,15 +1589,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110022988</v>
+        <v>110023980</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,7 +1619,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1769,13 +1629,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533440.7113318263</v>
+        <v>533282</v>
       </c>
       <c r="R11" t="n">
-        <v>6707135.662933774</v>
+        <v>6707254</v>
       </c>
       <c r="S11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1802,19 +1662,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,15 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110023249</v>
+        <v>110024385</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,7 +1721,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1886,13 +1731,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533437.9842615366</v>
+        <v>533291</v>
       </c>
       <c r="R12" t="n">
-        <v>6707163.722527532</v>
+        <v>6707216</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1919,19 +1764,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,15 +1793,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110023546</v>
+        <v>110024582</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1823,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2003,13 +1833,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533399.7590060034</v>
+        <v>533337</v>
       </c>
       <c r="R13" t="n">
-        <v>6707188.004893767</v>
+        <v>6707191</v>
       </c>
       <c r="S13" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2036,19 +1866,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 21926-2023 artfynd.xlsx
+++ b/artfynd/A 21926-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110023751</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109996780</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,6 +989,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109996845</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109996964</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110022988</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110023249</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110023546</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1484,6 +1524,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110023596</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110023746</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1688,6 +1738,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110023980</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1790,6 +1845,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110024385</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1892,8 +1952,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110024582</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>